--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:10</t>
+    <t xml:space="preserve">2026-09-09 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:07</t>
+    <t xml:space="preserve">2026-09-17 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>473423.97</v>
+        <v>408794.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>385324.84</v>
+        <v>473423.97</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>408794.03</v>
+        <v>385324.84</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>312231.62</v>
+        <v>360401.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>379893.59</v>
+        <v>398297.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>409024.62</v>
+        <v>408794.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>414068.28</v>
+        <v>312231.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>463106.28</v>
+        <v>379893.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>473423.97</v>
+        <v>409024.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>340114.97</v>
+        <v>414068.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>376921.69</v>
+        <v>463106.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>385324.84</v>
+        <v>473423.97</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>360401.69</v>
+        <v>340114.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>398297.44</v>
+        <v>376921.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>408794.03</v>
+        <v>385324.84</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:37</t>
+    <t xml:space="preserve">2026-09-25 21:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -539,7 +539,7 @@
         <v>239491.72</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1615.9</v>
+        <v>1615.91</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.67</v>
@@ -562,7 +562,7 @@
         <v>372265.34</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7470.82</v>
+        <v>7470.81</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2.01</v>
@@ -700,7 +700,7 @@
         <v>453260.44</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16987.15</v>
+        <v>16987.16</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>3.75</v>
@@ -723,7 +723,7 @@
         <v>362574.75</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12066.87</v>
+        <v>12066.88</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3.33</v>
@@ -792,7 +792,7 @@
         <v>376921.69</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8403.15</v>
+        <v>8403.16</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>2.23</v>
@@ -1045,7 +1045,7 @@
         <v>384238.66</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>35124.68</v>
+        <v>35124.69</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>9.14</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:35</t>
+    <t xml:space="preserve">2026-10-05 07:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -824,7 +824,7 @@
         <v>289731</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>487892</v>
+        <v>487893</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>-40.6</v>
